--- a/forecast/CTS Forecast Pack FY27 - actuals to September.xlsx
+++ b/forecast/CTS Forecast Pack FY27 - actuals to September.xlsx
@@ -16,10 +16,6 @@
   <definedNames>
     <definedName function="false" hidden="false" name="AcctName" vbProcedure="false">#REF!</definedName>
     <definedName function="false" hidden="false" name="AcctSubCate" vbProcedure="false">#REF!</definedName>
-    <definedName function="false" hidden="true" name="__xlchart.v1.0" vbProcedure="false">[2]summary!#ref!</definedName>
-    <definedName function="false" hidden="true" name="__xlchart.v1.1" vbProcedure="false">[2]summary!#ref!</definedName>
-    <definedName function="false" hidden="true" name="__xlchart.v1.2" vbProcedure="false">[2]summary!#ref!</definedName>
-    <definedName function="false" hidden="true" name="__xlchart.v1.3" vbProcedure="false">[2]summary!#ref!</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
